--- a/content-export/06_Contact_Us.xlsx
+++ b/content-export/06_Contact_Us.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,6 +168,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1922,15 +1923,19 @@
           <t>IR</t>
         </is>
       </c>
-      <c r="G29" s="8" t="n"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>IR / PR</t>
+        </is>
+      </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>IR / PR</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>값: ir — 이 값으로 수신 메일이 갈립니다('메일 발송' 시트 참고)</t>
+          <t>2026-10-23 변경 — 관리자 화면 'IR/PR' · 문의처 카드 'IR / PR' 과 맞춤 (값: ir 그대로)</t>
         </is>
       </c>
       <c r="J29" s="10" t="n"/>
@@ -2408,15 +2413,19 @@
           <t>문의가 접수되었습니다. 담당자가 확인 후 sales@aproele.com으로 답변 드리겠습니다.</t>
         </is>
       </c>
-      <c r="G42" s="8" t="n"/>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>문의가 접수되었습니다. 담당자가 확인 후 답변 드리겠습니다.</t>
+        </is>
+      </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>Your inquiry has been received. Our representative will review it and respond to sales@aproele.com.</t>
+          <t>Your inquiry has been received. Our representative will review it and respond.</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>문장 안에 sales@aproele.com 이 박혀 있음 — 결정된 수신 메일과 같으므로 그대로 쓰면 됩니다. 나중에 수신 메일을 바꾸면 이 문구도 함께 고쳐야 합니다</t>
+          <t>2026-10-23 변경 — 받는 주소는 관리자 설정을 따르므로 문구에서 주소를 뺌</t>
         </is>
       </c>
       <c r="J42" s="10" t="n"/>
@@ -3031,7 +3040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3088,7 +3097,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>IR / PR</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -3103,17 +3112,17 @@
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>ir@aproele.com</t>
+          <t>apro_ai@aproele.com, djjeong@aproele.com, yrheo@aproele.com</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>관리자 설정</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>화면 안내 기준으로 결정</t>
+          <t>관리자 화면(설정 &gt; 메일 설정) 2026-10-23 기준. apro_ai@ 포함 — 실제 수신자인지 확인 필요</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3154,12 @@
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>관리자 설정</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>화면에 협력 문의용 메일이 없습니다. 제품·기술과 같은 영업 창구로 보내는 안을 적어 두었습니다 — 담당자 확인 후 확정해 주세요.</t>
+          <t>관리자 화면(설정 &gt; 메일 설정) 2026-10-23 기준. 관리자 화면 값 끝에 쉼표가 남아 있음('sales@aproele.com,') — 지우거나 서버가 빈 주소를 걸러야 함</t>
         </is>
       </c>
     </row>
@@ -3177,17 +3186,17 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>recruit@aproele.com</t>
+          <t>apro_ai@aproele.com, msoh@aproele.com</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>관리자 설정</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>화면 안내 기준으로 결정</t>
+          <t>관리자 화면(설정 &gt; 메일 설정) 2026-10-23 기준. apro_ai@ 포함 — 실제 수신자인지 확인 필요</t>
         </is>
       </c>
     </row>
@@ -3214,17 +3223,17 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>sales@aproele.com</t>
+          <t>apro_ai@aproele.com, sangho.kim@aproele.com</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>관리자 설정</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>화면 안내 기준으로 결정</t>
+          <t>관리자 화면(설정 &gt; 메일 설정) 2026-10-23 기준. apro_ai@ 포함 — 실제 수신자인지 확인 필요</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3260,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>(미정)</t>
+          <t>apro_ai@aproele.com</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -3261,7 +3270,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>지속가능경영 &gt; 제보센터에서 쓰는 값입니다. 사이트에 메일이 공개되어 있지 않고, 제보자 익명·비밀 보장이 핵심이라 영업 창구와 분리하는 편이 맞습니다. 별도 주소를 정해 주세요.</t>
+          <t>관리자 화면(설정 &gt; 메일 설정) 2026-10-23 기준. 익명 · 비밀 보장 창구라 개발용 apro_ai@ 와 분리한 별도 주소 필요 — 결정 필요</t>
         </is>
       </c>
     </row>
@@ -3332,6 +3341,13 @@
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>⑤ 문의 내용은 DB 에 쌓이지 않고 메일로만 나갑니다 — 신규 사이트에서 접수 이력을 남기려면 따로 설계해야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23: 수신 메일은 관리자 화면(설정 &gt; 메일 설정)이 원본이다. 이 표는 그날 화면을 옮긴 것. 화면의 apro_ai@aproele.com 은 옛 사이트 개발 중 테스트 값이었다 — 남길지 확인.</t>
         </is>
       </c>
     </row>
